--- a/addons/purchase/static/xls/requests_for_quotation_import_template.xlsx
+++ b/addons/purchase/static/xls/requests_for_quotation_import_template.xlsx
@@ -91,7 +91,7 @@
     <t xml:space="preserve">P00003</t>
   </si>
   <si>
-    <t xml:space="preserve">Deco Addict</t>
+    <t xml:space="preserve">Acme Corporation</t>
   </si>
   <si>
     <t xml:space="preserve">REF161800</t>
